--- a/promocoes.xlsx
+++ b/promocoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael Castro\Documents\gerar-imagem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E30D1E2-0EE8-4D05-9BB8-A008452B6213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{634E7B20-43E7-4D0F-A22E-48A223E3FB74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{E5CF45C3-0614-48A6-8C4F-006EC199C177}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
   <si>
     <t>descricao</t>
   </si>
@@ -43,16 +43,64 @@
   </si>
   <si>
     <t>83.0943</t>
+  </si>
+  <si>
+    <t>BICICLETA  ARO 26 21V FIRST LIFTY TAM 17.5 AZUL GALAXY/ VERDE AMARELO - 55076</t>
+  </si>
+  <si>
+    <t>83.0944</t>
+  </si>
+  <si>
+    <t>peças</t>
+  </si>
+  <si>
+    <t>01.0000</t>
+  </si>
+  <si>
+    <t>01.0001</t>
+  </si>
+  <si>
+    <t>01.0002</t>
+  </si>
+  <si>
+    <t>01.0003</t>
+  </si>
+  <si>
+    <t>01.0004</t>
+  </si>
+  <si>
+    <t>01.0005</t>
+  </si>
+  <si>
+    <t>01.0006</t>
+  </si>
+  <si>
+    <t>01.0007</t>
+  </si>
+  <si>
+    <t>01.0008</t>
+  </si>
+  <si>
+    <t>01.0009</t>
+  </si>
+  <si>
+    <t>01.0010</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -395,10 +443,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A8FE7EE-E501-4B97-88C7-40543CDDBCF9}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" customWidth="1"/>
+    <col min="1" max="1" width="76.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -435,7 +483,140 @@
         <v>20</v>
       </c>
     </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/promocoes.xlsx
+++ b/promocoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael Castro\Documents\gerar-imagem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{634E7B20-43E7-4D0F-A22E-48A223E3FB74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46EE7E4D-C09E-428F-B8E0-68F5BC9E00D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{E5CF45C3-0614-48A6-8C4F-006EC199C177}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="19">
   <si>
     <t>descricao</t>
   </si>
@@ -39,21 +39,12 @@
     <t>83.0942</t>
   </si>
   <si>
-    <t>BICICLETA  ARO 29 21V FIRST LIFTY TAM 17.5 AZUL GALAXY/ VERDE AMARELO - 55076</t>
-  </si>
-  <si>
     <t>83.0943</t>
   </si>
   <si>
-    <t>BICICLETA  ARO 26 21V FIRST LIFTY TAM 17.5 AZUL GALAXY/ VERDE AMARELO - 55076</t>
-  </si>
-  <si>
     <t>83.0944</t>
   </si>
   <si>
-    <t>peças</t>
-  </si>
-  <si>
     <t>01.0000</t>
   </si>
   <si>
@@ -85,6 +76,12 @@
   </si>
   <si>
     <t>01.0010</t>
+  </si>
+  <si>
+    <t>valor_original</t>
+  </si>
+  <si>
+    <t>BICICLETA  ARO 29 21V FIRST LIFTY TAM 17.5 AZUL GALAXY</t>
   </si>
 </sst>
 </file>
@@ -443,14 +440,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A8FE7EE-E501-4B97-88C7-40543CDDBCF9}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="76.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="2" max="2" width="9.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -458,161 +457,206 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="C2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="D2">
+        <v>11.6666666666667</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="D3">
+        <v>16.6666666666667</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>100</v>
+      </c>
+      <c r="D4">
+        <v>21.6666666666667</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C5">
+        <v>100</v>
+      </c>
+      <c r="D5">
+        <v>26.6666666666667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>31.6666666666667</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C7">
+        <v>100</v>
+      </c>
+      <c r="D7">
+        <v>36.6666666666667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="C8">
+        <v>100</v>
+      </c>
+      <c r="D8">
+        <v>41.6666666666667</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="C9">
+        <v>100</v>
+      </c>
+      <c r="D9">
+        <v>46.6666666666667</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="C10">
+        <v>100</v>
+      </c>
+      <c r="D10">
+        <v>51.6666666666667</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="C11">
+        <v>100</v>
+      </c>
+      <c r="D11">
+        <v>56.6666666666667</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="C12">
+        <v>100</v>
+      </c>
+      <c r="D12">
+        <v>61.6666666666667</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="C13">
+        <v>100</v>
+      </c>
+      <c r="D13">
+        <v>66.6666666666667</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="C14">
+        <v>100</v>
+      </c>
+      <c r="D14">
+        <v>71.6666666666667</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="C15">
-        <v>2</v>
+        <v>100</v>
+      </c>
+      <c r="D15">
+        <v>76.6666666666667</v>
       </c>
     </row>
   </sheetData>

--- a/promocoes.xlsx
+++ b/promocoes.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael Castro\Documents\gerar-imagem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46EE7E4D-C09E-428F-B8E0-68F5BC9E00D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12BC40C2-02CC-4CEC-89D5-7DE8E251C2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{E5CF45C3-0614-48A6-8C4F-006EC199C177}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$D$62</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="126">
   <si>
     <t>descricao</t>
   </si>
@@ -39,56 +42,377 @@
     <t>83.0942</t>
   </si>
   <si>
-    <t>83.0943</t>
-  </si>
-  <si>
     <t>83.0944</t>
   </si>
   <si>
-    <t>01.0000</t>
-  </si>
-  <si>
-    <t>01.0001</t>
-  </si>
-  <si>
-    <t>01.0002</t>
-  </si>
-  <si>
-    <t>01.0003</t>
-  </si>
-  <si>
-    <t>01.0004</t>
-  </si>
-  <si>
-    <t>01.0005</t>
-  </si>
-  <si>
-    <t>01.0006</t>
-  </si>
-  <si>
-    <t>01.0007</t>
-  </si>
-  <si>
-    <t>01.0008</t>
-  </si>
-  <si>
-    <t>01.0009</t>
-  </si>
-  <si>
-    <t>01.0010</t>
-  </si>
-  <si>
     <t>valor_original</t>
   </si>
   <si>
-    <t>BICICLETA  ARO 29 21V FIRST LIFTY TAM 17.5 AZUL GALAXY</t>
+    <t>83.0446</t>
+  </si>
+  <si>
+    <t>83.0704</t>
+  </si>
+  <si>
+    <t>83.0414</t>
+  </si>
+  <si>
+    <t>83.0417</t>
+  </si>
+  <si>
+    <t>83.0411</t>
+  </si>
+  <si>
+    <t>83.0447</t>
+  </si>
+  <si>
+    <t>83.0425</t>
+  </si>
+  <si>
+    <t>83.0412</t>
+  </si>
+  <si>
+    <t>83.0705</t>
+  </si>
+  <si>
+    <t>83.0415</t>
+  </si>
+  <si>
+    <t>83.0829</t>
+  </si>
+  <si>
+    <t>83.0452</t>
+  </si>
+  <si>
+    <t>83.0422</t>
+  </si>
+  <si>
+    <t>83.0423</t>
+  </si>
+  <si>
+    <t>83.0680</t>
+  </si>
+  <si>
+    <t>83.0846</t>
+  </si>
+  <si>
+    <t>83.0957</t>
+  </si>
+  <si>
+    <t>83.0867</t>
+  </si>
+  <si>
+    <t>83.0875</t>
+  </si>
+  <si>
+    <t>83.0814</t>
+  </si>
+  <si>
+    <t>83.0877</t>
+  </si>
+  <si>
+    <t>83.0897</t>
+  </si>
+  <si>
+    <t>83.0856</t>
+  </si>
+  <si>
+    <t>83.0901</t>
+  </si>
+  <si>
+    <t>83.0782</t>
+  </si>
+  <si>
+    <t>83.0962</t>
+  </si>
+  <si>
+    <t>83.0960</t>
+  </si>
+  <si>
+    <t>83.0963</t>
+  </si>
+  <si>
+    <t>83.0959</t>
+  </si>
+  <si>
+    <t>83.0961</t>
+  </si>
+  <si>
+    <t>83.0956</t>
+  </si>
+  <si>
+    <t>83.0920</t>
+  </si>
+  <si>
+    <t>83.0918</t>
+  </si>
+  <si>
+    <t>83.0919</t>
+  </si>
+  <si>
+    <t>83.0939</t>
+  </si>
+  <si>
+    <t>83.0940</t>
+  </si>
+  <si>
+    <t>83.0923</t>
+  </si>
+  <si>
+    <t>83.0958</t>
+  </si>
+  <si>
+    <t>83.0952</t>
+  </si>
+  <si>
+    <t>83.0925</t>
+  </si>
+  <si>
+    <t>83.0500</t>
+  </si>
+  <si>
+    <t>83.0428</t>
+  </si>
+  <si>
+    <t>83.0841</t>
+  </si>
+  <si>
+    <t>83.0817</t>
+  </si>
+  <si>
+    <t>83.0795</t>
+  </si>
+  <si>
+    <t>83.0837</t>
+  </si>
+  <si>
+    <t>83.0818</t>
+  </si>
+  <si>
+    <t>83.0803</t>
+  </si>
+  <si>
+    <t>83.0892</t>
+  </si>
+  <si>
+    <t>83.0824</t>
+  </si>
+  <si>
+    <t>83.0825</t>
+  </si>
+  <si>
+    <t>83.0965</t>
+  </si>
+  <si>
+    <t>83.0964</t>
+  </si>
+  <si>
+    <t>83.0930</t>
+  </si>
+  <si>
+    <t>83.0966</t>
+  </si>
+  <si>
+    <t>83.0926</t>
+  </si>
+  <si>
+    <t>83.0953</t>
+  </si>
+  <si>
+    <t>83.0967</t>
+  </si>
+  <si>
+    <t>83.0934</t>
+  </si>
+  <si>
+    <t>BIC 26 AL VIKING DIRT J.TUFF X-25 AZUL/AMARELO</t>
+  </si>
+  <si>
+    <t>BIC 26 AL VIKING DIRT J.TUFF X-25 BRANCO/VERDE</t>
+  </si>
+  <si>
+    <t>BIC 26 AL VIKING DIRT J.TUFF X-25 PRATA/AZUL</t>
+  </si>
+  <si>
+    <t>BIC 26 AL VIKING DIRT J.TUFF X-25 PRETO/AMARELO</t>
+  </si>
+  <si>
+    <t>BIC 26 AL VIKING DIRT J.TUFF X-25 PRETO/ROSA</t>
+  </si>
+  <si>
+    <t>BIC 26 AL VIKING DIRT J.TUFF X-25 ROSA/AZUL</t>
+  </si>
+  <si>
+    <t>BIC 26 AL VIKING DIRT J.TUFF X-25 ROXO/AMARELO</t>
+  </si>
+  <si>
+    <t>BIC 26 AL VIKING DIRT J.TUFF X-25 ROXO/LARANJA</t>
+  </si>
+  <si>
+    <t>BIC 26 AL VIKING DIRT J.TUFF X-25 VERDE NEON</t>
+  </si>
+  <si>
+    <t>BIC 26 AL VIKING DIRT J.TUFF X-25 VERMELHO</t>
+  </si>
+  <si>
+    <t>BIC 26 AL VIKING DIRT J.TUFF X-25 VERMELHO/ AZUL</t>
+  </si>
+  <si>
+    <t>BIC 26 AL VIKING DIRT J.TUFF X-30 AZUL</t>
+  </si>
+  <si>
+    <t>BIC 26 AL VIKING DIRT J.TUFF X-30 LARANJA</t>
+  </si>
+  <si>
+    <t>BIC 26 AL VIKING DIRT J.TUFF X-30 VERDE NEON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BICICLETA ARO 29 21V FIRST TAM 15,5 OURO/PTO SMITT </t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V FIRST TAM 15.5 AZUL GALAXY/ BRANCO LIFTY - 54779</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V FIRST TAM 15.5 FIRST FEM BRANCO/ LARANJA E AMARELO LIFTY - 51743</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST BEGE/ AZUL E ROXO LIFTY - 54766</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST 17.5 BEGE/ VERMELHO LIFTY  - 54782</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST BRANCO/ROSA LIFTY - 48598</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FOSCO GRAFITE/ PRATA LIFTY - 46904</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FOSCO GRAFITE/ VERDE E ROXO LIFTY - 54854</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FOSCO VERMELHO/ CHUMBO LIFTY - 46035</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST GRAFITE/ VERDE E ROXO LIFTY - 54806</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST GRAFITE/VERDE/AMARELO LIFTY - 46659</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM  17.5 FIRST CINZA/ CHUMBO LIFTY - 51208</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST AZUL ZIMBRO/ CHUMBO LIFTY - 49214</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST BRANCO/ ROXO LIFTY - 54798</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST CINZA/ AZUL E ROXO LIFTY - 54826</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FEM AZUL CAPRI/ PRATA LIFTY - 54565</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FEM LARANJA CHICLETE/ BRANCO LIFTY - 55433</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FEM LILAS/ CHUMBO LIFTY - 55507</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FOSCO PRETO/ AZUL TIFFANY - 50619</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FOSCO PRETO/ CHUMBO - 49415</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FOSCO VERMELHO/ BRANCO E PRATA - 55374</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST FOSCO VERMELHO/ PRATA LIFTY - 55381</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST GRAFITE/ CHUMBO LIFTY - 46030</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST PRETO/ VERDE E AMARELO LIFTY - 46243</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST VERDE MILITAR/ AZUL E ROXO LIFTY - 54758</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST VERDE MILITAR/ CHUMBO LIFTY - 48552</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 17.5 FIRST VERMELHO/ PRATA - 55240</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST AZUL GALAXY/VERMELHO LIFTY - 54773</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST  AZUL HUNTER/PRATA LIFTY - 47904</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST BRANCO/BRITO LIFTY - 48447</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST BRANCO/LARANJA/AMARELO LIFTY - 49318</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST PRATA/CHUMBO LIFTY - 47026</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST PRETO/AMARELO/LARANJA LIFTY - 48753</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM 21 FOSCO VERMELHO/CHUMBO - 47805</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V FIRST LIFTY TAM19 VERDE CHICLETE/CHUMBO - 52328</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST AZUL HUNTER/ CHUMBO LIFTY - 49094</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST FOSCO PRATA/ CHUMBO LIFTY - 47028</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST FOSCO PRETO/VERDE/AMARELO LIFTY - 50621</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST FOSCO VERDE MILITAR/ AZUL E ROXO LIFTY - 54833</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST PRETO/ BRITO LIFTY - 48004</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST VERDE MILITAR/ PRATA LIFTY - 49464</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST VERMELHO/ BRANCO E PRATA LIFTY - 55194</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 21 FIRST VERDE MILITAR/ PRATA LIFTY - 49421</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 24V K7 FIRST LIFTY TAM 17.5 FOSCO GRAFITE/ PRATA - 46904</t>
+  </si>
+  <si>
+    <t>BICICLETA  ARO 29 21V FIRST LIFTY TAM 21 AZUL GALAXY/ VERMELHO - 54772</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST PRETO F/TIFFANY SMITT KIT1</t>
+  </si>
+  <si>
+    <t>BICICLETA ARO 29 21V TAM 19 FIRST PTO/LILAS/PESSEGO SMITT KIT1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,6 +425,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -123,9 +453,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -440,7 +773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A8FE7EE-E501-4B97-88C7-40543CDDBCF9}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="76.140625" bestFit="1" customWidth="1"/>
@@ -457,7 +790,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -465,201 +798,867 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>100</v>
-      </c>
-      <c r="D2">
-        <v>11.6666666666667</v>
+        <v>65</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1145.5</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1064.26</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>100</v>
-      </c>
-      <c r="D3">
-        <v>16.6666666666667</v>
+        <v>66</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1145.5</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1064.26</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>100</v>
-      </c>
-      <c r="D4">
-        <v>21.6666666666667</v>
+        <v>67</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1145.5</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1064.26</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5">
-        <v>100</v>
-      </c>
-      <c r="D5">
-        <v>26.6666666666667</v>
+        <v>68</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1145.5</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1064.26</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6">
-        <v>100</v>
-      </c>
-      <c r="D6">
-        <v>31.6666666666667</v>
+        <v>69</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1145.5</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1064.26</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7">
-        <v>100</v>
-      </c>
-      <c r="D7">
-        <v>36.6666666666667</v>
+        <v>70</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1145.5</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1064.26</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8">
-        <v>100</v>
-      </c>
-      <c r="D8">
-        <v>41.6666666666667</v>
+        <v>71</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1145.5</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1064.26</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9">
-        <v>100</v>
-      </c>
-      <c r="D9">
-        <v>46.6666666666667</v>
+        <v>72</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1145.5</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1064.26</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10">
-        <v>100</v>
-      </c>
-      <c r="D10">
-        <v>51.6666666666667</v>
+        <v>73</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1145.5</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1064.26</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11">
-        <v>100</v>
-      </c>
-      <c r="D11">
-        <v>56.6666666666667</v>
+        <v>74</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1145.5</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1064.26</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12">
-        <v>100</v>
-      </c>
-      <c r="D12">
-        <v>61.6666666666667</v>
+        <v>75</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1145.5</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1064.26</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13">
-        <v>100</v>
-      </c>
-      <c r="D13">
-        <v>66.6666666666667</v>
+        <v>76</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1145.5</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1064.26</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14">
-        <v>100</v>
-      </c>
-      <c r="D14">
-        <v>71.6666666666667</v>
+      <c r="C14" s="2">
+        <v>1145.5</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1064.26</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15">
+        <v>78</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1145.5</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1064.26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>123</v>
+      </c>
+      <c r="B16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D16" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>112</v>
+      </c>
+      <c r="B17" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D17" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>113</v>
+      </c>
+      <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D18" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D19" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D20" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D21" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D22" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D23" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D24" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D25" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D26" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D27" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>93</v>
+      </c>
+      <c r="B28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D28" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>94</v>
+      </c>
+      <c r="B29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D29" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>95</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D30" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D31" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D32" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D33" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>97</v>
+      </c>
+      <c r="B34" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D34" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D35" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>99</v>
+      </c>
+      <c r="B36" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D36" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>87</v>
+      </c>
+      <c r="B37" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D37" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>100</v>
       </c>
-      <c r="D15">
-        <v>76.6666666666667</v>
-      </c>
+      <c r="B38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D38" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>101</v>
+      </c>
+      <c r="B39" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D39" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>88</v>
+      </c>
+      <c r="B40" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D40" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>89</v>
+      </c>
+      <c r="B41" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D41" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>102</v>
+      </c>
+      <c r="B42" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D42" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>103</v>
+      </c>
+      <c r="B43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D43" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>104</v>
+      </c>
+      <c r="B44" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D44" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>105</v>
+      </c>
+      <c r="B45" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D45" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>107</v>
+      </c>
+      <c r="B46" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D46" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>106</v>
+      </c>
+      <c r="B47" t="s">
+        <v>48</v>
+      </c>
+      <c r="C47" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D47" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>114</v>
+      </c>
+      <c r="B48" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D48" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>108</v>
+      </c>
+      <c r="B49" t="s">
+        <v>50</v>
+      </c>
+      <c r="C49" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D49" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>109</v>
+      </c>
+      <c r="B50" t="s">
+        <v>51</v>
+      </c>
+      <c r="C50" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D50" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>115</v>
+      </c>
+      <c r="B51" t="s">
+        <v>58</v>
+      </c>
+      <c r="C51" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D51" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>116</v>
+      </c>
+      <c r="B52" t="s">
+        <v>59</v>
+      </c>
+      <c r="C52" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D52" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>117</v>
+      </c>
+      <c r="B53" t="s">
+        <v>60</v>
+      </c>
+      <c r="C53" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D53" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>110</v>
+      </c>
+      <c r="B54" t="s">
+        <v>52</v>
+      </c>
+      <c r="C54" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D54" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>118</v>
+      </c>
+      <c r="B55" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D55" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>111</v>
+      </c>
+      <c r="B56" t="s">
+        <v>53</v>
+      </c>
+      <c r="C56" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D56" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>119</v>
+      </c>
+      <c r="B57" t="s">
+        <v>62</v>
+      </c>
+      <c r="C57" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D57" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>120</v>
+      </c>
+      <c r="B58" t="s">
+        <v>63</v>
+      </c>
+      <c r="C58" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D58" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>121</v>
+      </c>
+      <c r="B59" t="s">
+        <v>64</v>
+      </c>
+      <c r="C59" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D59" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>122</v>
+      </c>
+      <c r="B60" t="s">
+        <v>4</v>
+      </c>
+      <c r="C60" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D60" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>124</v>
+      </c>
+      <c r="B61" t="s">
+        <v>46</v>
+      </c>
+      <c r="C61" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D61" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>125</v>
+      </c>
+      <c r="B62" t="s">
+        <v>47</v>
+      </c>
+      <c r="C62" s="3">
+        <v>733.64</v>
+      </c>
+      <c r="D62" s="2">
+        <v>692.63</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="4"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D62" xr:uid="{0A8FE7EE-E501-4B97-88C7-40543CDDBCF9}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D62">
+      <sortCondition ref="A1:A62"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/promocoes.xlsx
+++ b/promocoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael Castro\Documents\gerar-imagem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72FA30E3-0B9B-429D-9F8F-2AA0B51BCC98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7927C9CE-67EE-454A-80B4-B42450CA1AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{E5CF45C3-0614-48A6-8C4F-006EC199C177}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>descricao</t>
   </si>
@@ -42,10 +42,130 @@
     <t>valor_original</t>
   </si>
   <si>
-    <t>42.0042</t>
-  </si>
-  <si>
     <t>PATINS MTB VB CH10 POWER 70MM</t>
+  </si>
+  <si>
+    <t>12.0062</t>
+  </si>
+  <si>
+    <t>70.0011</t>
+  </si>
+  <si>
+    <t>46.0043</t>
+  </si>
+  <si>
+    <t>46.0042</t>
+  </si>
+  <si>
+    <t>15.0121</t>
+  </si>
+  <si>
+    <t>44.0010</t>
+  </si>
+  <si>
+    <t>20.0001</t>
+  </si>
+  <si>
+    <t>44.0041</t>
+  </si>
+  <si>
+    <t>04.0120</t>
+  </si>
+  <si>
+    <t>03.0099</t>
+  </si>
+  <si>
+    <t>07.0087</t>
+  </si>
+  <si>
+    <t>15.0124</t>
+  </si>
+  <si>
+    <t>04.0062</t>
+  </si>
+  <si>
+    <t>04.0212</t>
+  </si>
+  <si>
+    <t>23.0130</t>
+  </si>
+  <si>
+    <t>04.0177</t>
+  </si>
+  <si>
+    <t>04.0189</t>
+  </si>
+  <si>
+    <t>23.0128</t>
+  </si>
+  <si>
+    <t>23.0127</t>
+  </si>
+  <si>
+    <t>04.0135</t>
+  </si>
+  <si>
+    <t>21.0067</t>
+  </si>
+  <si>
+    <t>KIT 2X9 SHIMANO ALIVIO   FREIO HIDRAULICO MT200 - CUBO 32F</t>
+  </si>
+  <si>
+    <t>LIMPEZA GERAL SOLIFES 500ML</t>
+  </si>
+  <si>
+    <t>PATINS MTB VB ORBITAL 70MM GTS (BLISTER)</t>
+  </si>
+  <si>
+    <t>RODA LIVRE 20D COMANDER</t>
+  </si>
+  <si>
+    <t>GARFO 26 S. 21.1 MODE PTO</t>
+  </si>
+  <si>
+    <t>PEDIV 165MM R CICLO CROM</t>
+  </si>
+  <si>
+    <t>GARFO 29 S. AH SET ACO TAIWAN PTO</t>
+  </si>
+  <si>
+    <t>SELIM BEACH 2M INVIKTUS PTO C/ REFLETOR</t>
+  </si>
+  <si>
+    <t>CAMARA 26 BUTIL BISON (CAIXA FECHADA)</t>
+  </si>
+  <si>
+    <t>PASTILHA REFIL GTS QUAD. C/MOLA F DISCO PAR (GRANEL)</t>
+  </si>
+  <si>
+    <t>RODA LIVRE 7V INDEX FALCON 14/28 BRONZE</t>
+  </si>
+  <si>
+    <t>SELIM MTB VAZ INVIKTUS PTO</t>
+  </si>
+  <si>
+    <t>SELIM MTB VAZ GTS HY-298 NEO PTO</t>
+  </si>
+  <si>
+    <t>MANOPLA FREERIDE MOOVE VERMELHO 165MM C/ FLANGE</t>
+  </si>
+  <si>
+    <t>SELIM MTB NITRUS BELUGA C/CAR PTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELIM BEACH 2M LTX186-1 PTO C/CAR </t>
+  </si>
+  <si>
+    <t>MANOPLA FREERIDE MOOVE LARANJA 165MM C/ FLANGE</t>
+  </si>
+  <si>
+    <t>MANOPLA FREERIDE MOOVE ROSA 165MM C/ FLANGE</t>
+  </si>
+  <si>
+    <t>SELIM SRX HAVAC VAZ R CICLO PTO</t>
+  </si>
+  <si>
+    <t>CUBO D/T AL ROLLER VIPER PTO</t>
   </si>
 </sst>
 </file>
@@ -70,10 +190,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF333333"/>
-      <name val="Segoe UI"/>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -99,16 +221,16 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -423,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A8FE7EE-E501-4B97-88C7-40543CDDBCF9}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="76.140625" bestFit="1" customWidth="1"/>
@@ -446,99 +568,299 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="5">
+        <v>1138</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1115.24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="5">
+        <v>15.42</v>
+      </c>
+      <c r="D3" s="5">
+        <v>14.9574</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1.43</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1.3871</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3">
-        <v>2.21</v>
-      </c>
-      <c r="D2" s="2">
-        <v>2.13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B3" s="2"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B4" s="2"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B5" s="2"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B6" s="2"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B7" s="2"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B8" s="2"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="2"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="2"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="2"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="2"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="2"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="2"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="2"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="2"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" s="2"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="2"/>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="5">
+        <v>2.2138999999999998</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2.1253439999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5">
+        <v>5.9735999999999994</v>
+      </c>
+      <c r="D6" s="5">
+        <v>5.7346559999999993</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="5">
+        <v>51.92</v>
+      </c>
+      <c r="D7" s="5">
+        <v>49.843200000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="5">
+        <v>16.989999999999998</v>
+      </c>
+      <c r="D8" s="5">
+        <v>16.310399999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="5">
+        <v>48.59</v>
+      </c>
+      <c r="D9" s="5">
+        <v>46.6464</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="5">
+        <v>23.82</v>
+      </c>
+      <c r="D10" s="5">
+        <v>22.8672</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="5">
+        <v>6.99</v>
+      </c>
+      <c r="D11" s="5">
+        <v>6.5009700000000006</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1.9649999999999999</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1.8274499999999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="5">
+        <v>22.008000000000003</v>
+      </c>
+      <c r="D13" s="5">
+        <v>20.247360000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="5">
+        <v>23.841999999999999</v>
+      </c>
+      <c r="D14" s="5">
+        <v>21.934639999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="5">
+        <v>19.623799999999999</v>
+      </c>
+      <c r="D15" s="5">
+        <v>18.053895999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="5">
+        <v>7.5979999999999999</v>
+      </c>
+      <c r="D16" s="5">
+        <v>6.9901599999999995</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="5">
+        <v>19.623799999999999</v>
+      </c>
+      <c r="D17" s="5">
+        <v>18.053895999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="5">
+        <v>41.278100000000002</v>
+      </c>
+      <c r="D18" s="5">
+        <v>37.975852000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="5">
+        <v>7.5979999999999999</v>
+      </c>
+      <c r="D19" s="5">
+        <v>6.9901599999999995</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="5">
+        <v>7.5979999999999999</v>
+      </c>
+      <c r="D20" s="5">
+        <v>6.9901599999999995</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="5">
+        <v>74.997500000000002</v>
+      </c>
+      <c r="D21" s="5">
+        <v>68.997700000000009</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="5">
+        <v>34.06</v>
+      </c>
+      <c r="D22" s="5">
+        <v>31.3352</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D18" xr:uid="{0A8FE7EE-E501-4B97-88C7-40543CDDBCF9}"/>

--- a/promocoes.xlsx
+++ b/promocoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael Castro\Documents\gerar-imagem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7927C9CE-67EE-454A-80B4-B42450CA1AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8262F28-D1EE-4821-9B20-440A2C384991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{E5CF45C3-0614-48A6-8C4F-006EC199C177}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$D$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>descricao</t>
   </si>
@@ -42,42 +42,21 @@
     <t>valor_original</t>
   </si>
   <si>
-    <t>PATINS MTB VB CH10 POWER 70MM</t>
-  </si>
-  <si>
     <t>12.0062</t>
   </si>
   <si>
     <t>70.0011</t>
   </si>
   <si>
-    <t>46.0043</t>
-  </si>
-  <si>
-    <t>46.0042</t>
-  </si>
-  <si>
-    <t>15.0121</t>
-  </si>
-  <si>
     <t>44.0010</t>
   </si>
   <si>
-    <t>20.0001</t>
-  </si>
-  <si>
-    <t>44.0041</t>
-  </si>
-  <si>
     <t>04.0120</t>
   </si>
   <si>
     <t>03.0099</t>
   </si>
   <si>
-    <t>07.0087</t>
-  </si>
-  <si>
     <t>15.0124</t>
   </si>
   <si>
@@ -105,67 +84,70 @@
     <t>04.0135</t>
   </si>
   <si>
-    <t>21.0067</t>
-  </si>
-  <si>
-    <t>KIT 2X9 SHIMANO ALIVIO   FREIO HIDRAULICO MT200 - CUBO 32F</t>
-  </si>
-  <si>
-    <t>LIMPEZA GERAL SOLIFES 500ML</t>
-  </si>
-  <si>
-    <t>PATINS MTB VB ORBITAL 70MM GTS (BLISTER)</t>
-  </si>
-  <si>
-    <t>RODA LIVRE 20D COMANDER</t>
-  </si>
-  <si>
-    <t>GARFO 26 S. 21.1 MODE PTO</t>
-  </si>
-  <si>
-    <t>PEDIV 165MM R CICLO CROM</t>
-  </si>
-  <si>
-    <t>GARFO 29 S. AH SET ACO TAIWAN PTO</t>
-  </si>
-  <si>
-    <t>SELIM BEACH 2M INVIKTUS PTO C/ REFLETOR</t>
-  </si>
-  <si>
-    <t>CAMARA 26 BUTIL BISON (CAIXA FECHADA)</t>
-  </si>
-  <si>
-    <t>PASTILHA REFIL GTS QUAD. C/MOLA F DISCO PAR (GRANEL)</t>
-  </si>
-  <si>
-    <t>RODA LIVRE 7V INDEX FALCON 14/28 BRONZE</t>
-  </si>
-  <si>
-    <t>SELIM MTB VAZ INVIKTUS PTO</t>
-  </si>
-  <si>
-    <t>SELIM MTB VAZ GTS HY-298 NEO PTO</t>
-  </si>
-  <si>
-    <t>MANOPLA FREERIDE MOOVE VERMELHO 165MM C/ FLANGE</t>
-  </si>
-  <si>
-    <t>SELIM MTB NITRUS BELUGA C/CAR PTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELIM BEACH 2M LTX186-1 PTO C/CAR </t>
-  </si>
-  <si>
-    <t>MANOPLA FREERIDE MOOVE LARANJA 165MM C/ FLANGE</t>
-  </si>
-  <si>
-    <t>MANOPLA FREERIDE MOOVE ROSA 165MM C/ FLANGE</t>
-  </si>
-  <si>
-    <t>SELIM SRX HAVAC VAZ R CICLO PTO</t>
-  </si>
-  <si>
-    <t>CUBO D/T AL ROLLER VIPER PTO</t>
+    <t>20.0115</t>
+  </si>
+  <si>
+    <t>21.0115</t>
+  </si>
+  <si>
+    <t>44.0734</t>
+  </si>
+  <si>
+    <t>46.0054</t>
+  </si>
+  <si>
+    <t>RODA  LIVRE 7V INDEX FALCON 14/28 BRONZE</t>
+  </si>
+  <si>
+    <t>SELIM  MTB VAZ INVIKTUS PTO</t>
+  </si>
+  <si>
+    <t>SELIM  MTB VAZ GTS HY-298 NEO PTO</t>
+  </si>
+  <si>
+    <t>MANOPLA  FREERIDE MOOVE VERMELHO 165MM C/ FLANGE</t>
+  </si>
+  <si>
+    <t>GARFO  26 S. 21.1 MODE PTO</t>
+  </si>
+  <si>
+    <t>SELIM  MTB NITRUS BELUGA C/CAR PTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELIM  BEACH 2M LTX186-1 PTO C/CAR </t>
+  </si>
+  <si>
+    <t>MANOPLA  FREERIDE MOOVE LARANJA 165MM C/ FLANGE</t>
+  </si>
+  <si>
+    <t>MANOPLA  FREERIDE MOOVE ROSA 165MM C/ FLANGE</t>
+  </si>
+  <si>
+    <t>SELIM  SRX HAVAC VAZ R CICLO PTO</t>
+  </si>
+  <si>
+    <t>KIT  2X9 SHIMANO ALIVIO   FREIO HIDRAULICO MT200 - CUBO 32F</t>
+  </si>
+  <si>
+    <t>LIMPEZA  GERAL SOLIFES 500ML</t>
+  </si>
+  <si>
+    <t>PEDIV  165MM R CICLO CROM (CX FECHADA)</t>
+  </si>
+  <si>
+    <t>CUBO  D/T AL ROLLER VIPER PTO (CX FECHADA)</t>
+  </si>
+  <si>
+    <t>GARFO  29 S. AH SET ACO TAIWAN PTO (CX FECHADA)</t>
+  </si>
+  <si>
+    <t>CAMARA  26 BUTIL BISON (CAIXA FECHADA)</t>
+  </si>
+  <si>
+    <t>SELIM  BEACH 2M INVIKTUS PTO C/ REFLETOR</t>
+  </si>
+  <si>
+    <t>PATINS  MTB VB ORBITAL 70MM GTS (BLISTER) - (100 PARES)</t>
   </si>
 </sst>
 </file>
@@ -173,9 +155,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,6 +167,13 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -206,7 +195,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -214,25 +203,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -545,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A8FE7EE-E501-4B97-88C7-40543CDDBCF9}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="76.140625" bestFit="1" customWidth="1"/>
@@ -569,301 +572,259 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="4">
+        <v>22.007999999999999</v>
+      </c>
+      <c r="D2" s="4">
+        <v>20.247360000000004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4">
+        <v>23.841999999999999</v>
+      </c>
+      <c r="D3" s="4">
+        <v>21.934639999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="4">
+        <v>19.623799999999999</v>
+      </c>
+      <c r="D4" s="4">
+        <v>18.053895999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="4">
+        <v>7.5979999999999999</v>
+      </c>
+      <c r="D5" s="4">
+        <v>6.9901599999999995</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="4">
+        <v>51.92</v>
+      </c>
+      <c r="D6" s="4">
+        <v>49.843200000000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="4">
+        <v>19.623799999999999</v>
+      </c>
+      <c r="D7" s="4">
+        <v>18.053895999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="4">
+        <v>41.278100000000002</v>
+      </c>
+      <c r="D8" s="4">
+        <v>37.975852000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="4">
+        <v>7.5979999999999999</v>
+      </c>
+      <c r="D9" s="4">
+        <v>6.9901599999999995</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="4">
+        <v>7.5979999999999999</v>
+      </c>
+      <c r="D10" s="4">
+        <v>6.9901599999999995</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="4">
+        <v>74.997500000000002</v>
+      </c>
+      <c r="D11" s="4">
+        <v>68.997700000000009</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1138</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1115.24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="5">
-        <v>1138</v>
-      </c>
-      <c r="D2" s="5">
-        <v>1115.24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="5">
+      <c r="C13" s="4">
         <v>15.42</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D13" s="4">
         <v>14.9574</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="3" t="s">
+    <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="4">
+        <v>16.989999999999998</v>
+      </c>
+      <c r="D14" s="4">
+        <v>16.310399999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="4">
+        <v>34.06</v>
+      </c>
+      <c r="D15" s="4">
+        <v>31.3352</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="4">
+        <v>48.59</v>
+      </c>
+      <c r="D16" s="4">
+        <v>46.6464</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="4">
+        <v>6.99</v>
+      </c>
+      <c r="D17" s="4">
+        <v>6.5009700000000006</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C18" s="4">
+        <v>23.82</v>
+      </c>
+      <c r="D18" s="4">
+        <v>22.8672</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="4">
         <v>1.43</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D19" s="4">
         <v>1.3871</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="5">
-        <v>2.2138999999999998</v>
-      </c>
-      <c r="D5" s="5">
-        <v>2.1253439999999997</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="5">
-        <v>5.9735999999999994</v>
-      </c>
-      <c r="D6" s="5">
-        <v>5.7346559999999993</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="5">
-        <v>51.92</v>
-      </c>
-      <c r="D7" s="5">
-        <v>49.843200000000003</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="5">
-        <v>16.989999999999998</v>
-      </c>
-      <c r="D8" s="5">
-        <v>16.310399999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="5">
-        <v>48.59</v>
-      </c>
-      <c r="D9" s="5">
-        <v>46.6464</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="5">
-        <v>23.82</v>
-      </c>
-      <c r="D10" s="5">
-        <v>22.8672</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="5">
-        <v>6.99</v>
-      </c>
-      <c r="D11" s="5">
-        <v>6.5009700000000006</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="5">
-        <v>1.9649999999999999</v>
-      </c>
-      <c r="D12" s="5">
-        <v>1.8274499999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="5">
-        <v>22.008000000000003</v>
-      </c>
-      <c r="D13" s="5">
-        <v>20.247360000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="5">
-        <v>23.841999999999999</v>
-      </c>
-      <c r="D14" s="5">
-        <v>21.934639999999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="5">
-        <v>19.623799999999999</v>
-      </c>
-      <c r="D15" s="5">
-        <v>18.053895999999998</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="5">
-        <v>7.5979999999999999</v>
-      </c>
-      <c r="D16" s="5">
-        <v>6.9901599999999995</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="5">
-        <v>19.623799999999999</v>
-      </c>
-      <c r="D17" s="5">
-        <v>18.053895999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="5">
-        <v>41.278100000000002</v>
-      </c>
-      <c r="D18" s="5">
-        <v>37.975852000000003</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="5">
-        <v>7.5979999999999999</v>
-      </c>
-      <c r="D19" s="5">
-        <v>6.9901599999999995</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="5">
-        <v>7.5979999999999999</v>
-      </c>
-      <c r="D20" s="5">
-        <v>6.9901599999999995</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="5">
-        <v>74.997500000000002</v>
-      </c>
-      <c r="D21" s="5">
-        <v>68.997700000000009</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="5">
-        <v>34.06</v>
-      </c>
-      <c r="D22" s="5">
-        <v>31.3352</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D18" xr:uid="{0A8FE7EE-E501-4B97-88C7-40543CDDBCF9}"/>
+  <autoFilter ref="A1:D1" xr:uid="{0A8FE7EE-E501-4B97-88C7-40543CDDBCF9}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/promocoes.xlsx
+++ b/promocoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael Castro\Documents\gerar-imagem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8262F28-D1EE-4821-9B20-440A2C384991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1BAC493-5FF9-4E10-8DBD-CC668C30D97F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{E5CF45C3-0614-48A6-8C4F-006EC199C177}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>descricao</t>
   </si>
@@ -42,112 +42,10 @@
     <t>valor_original</t>
   </si>
   <si>
-    <t>12.0062</t>
-  </si>
-  <si>
-    <t>70.0011</t>
-  </si>
-  <si>
-    <t>44.0010</t>
-  </si>
-  <si>
-    <t>04.0120</t>
+    <t>CAMARA 26 BUTIL BISON (CAIXA FECHADA)</t>
   </si>
   <si>
     <t>03.0099</t>
-  </si>
-  <si>
-    <t>15.0124</t>
-  </si>
-  <si>
-    <t>04.0062</t>
-  </si>
-  <si>
-    <t>04.0212</t>
-  </si>
-  <si>
-    <t>23.0130</t>
-  </si>
-  <si>
-    <t>04.0177</t>
-  </si>
-  <si>
-    <t>04.0189</t>
-  </si>
-  <si>
-    <t>23.0128</t>
-  </si>
-  <si>
-    <t>23.0127</t>
-  </si>
-  <si>
-    <t>04.0135</t>
-  </si>
-  <si>
-    <t>20.0115</t>
-  </si>
-  <si>
-    <t>21.0115</t>
-  </si>
-  <si>
-    <t>44.0734</t>
-  </si>
-  <si>
-    <t>46.0054</t>
-  </si>
-  <si>
-    <t>RODA  LIVRE 7V INDEX FALCON 14/28 BRONZE</t>
-  </si>
-  <si>
-    <t>SELIM  MTB VAZ INVIKTUS PTO</t>
-  </si>
-  <si>
-    <t>SELIM  MTB VAZ GTS HY-298 NEO PTO</t>
-  </si>
-  <si>
-    <t>MANOPLA  FREERIDE MOOVE VERMELHO 165MM C/ FLANGE</t>
-  </si>
-  <si>
-    <t>GARFO  26 S. 21.1 MODE PTO</t>
-  </si>
-  <si>
-    <t>SELIM  MTB NITRUS BELUGA C/CAR PTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELIM  BEACH 2M LTX186-1 PTO C/CAR </t>
-  </si>
-  <si>
-    <t>MANOPLA  FREERIDE MOOVE LARANJA 165MM C/ FLANGE</t>
-  </si>
-  <si>
-    <t>MANOPLA  FREERIDE MOOVE ROSA 165MM C/ FLANGE</t>
-  </si>
-  <si>
-    <t>SELIM  SRX HAVAC VAZ R CICLO PTO</t>
-  </si>
-  <si>
-    <t>KIT  2X9 SHIMANO ALIVIO   FREIO HIDRAULICO MT200 - CUBO 32F</t>
-  </si>
-  <si>
-    <t>LIMPEZA  GERAL SOLIFES 500ML</t>
-  </si>
-  <si>
-    <t>PEDIV  165MM R CICLO CROM (CX FECHADA)</t>
-  </si>
-  <si>
-    <t>CUBO  D/T AL ROLLER VIPER PTO (CX FECHADA)</t>
-  </si>
-  <si>
-    <t>GARFO  29 S. AH SET ACO TAIWAN PTO (CX FECHADA)</t>
-  </si>
-  <si>
-    <t>CAMARA  26 BUTIL BISON (CAIXA FECHADA)</t>
-  </si>
-  <si>
-    <t>SELIM  BEACH 2M INVIKTUS PTO C/ REFLETOR</t>
-  </si>
-  <si>
-    <t>PATINS  MTB VB ORBITAL 70MM GTS (BLISTER) - (100 PARES)</t>
   </si>
 </sst>
 </file>
@@ -179,12 +77,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <sz val="9"/>
+      <color rgb="FF212121"/>
+      <name val="Segoe UI"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -195,7 +91,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -203,36 +99,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -548,7 +426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A8FE7EE-E501-4B97-88C7-40543CDDBCF9}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="76.140625" bestFit="1" customWidth="1"/>
@@ -571,256 +449,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="4">
-        <v>22.007999999999999</v>
-      </c>
-      <c r="D2" s="4">
-        <v>20.247360000000004</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="4">
-        <v>23.841999999999999</v>
-      </c>
-      <c r="D3" s="4">
-        <v>21.934639999999998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="4">
-        <v>19.623799999999999</v>
-      </c>
-      <c r="D4" s="4">
-        <v>18.053895999999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="4">
-        <v>7.5979999999999999</v>
-      </c>
-      <c r="D5" s="4">
-        <v>6.9901599999999995</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="4">
-        <v>51.92</v>
-      </c>
-      <c r="D6" s="4">
-        <v>49.843200000000003</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="4">
-        <v>19.623799999999999</v>
-      </c>
-      <c r="D7" s="4">
-        <v>18.053895999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="4">
-        <v>41.278100000000002</v>
-      </c>
-      <c r="D8" s="4">
-        <v>37.975852000000003</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="4">
-        <v>7.5979999999999999</v>
-      </c>
-      <c r="D9" s="4">
-        <v>6.9901599999999995</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="4">
-        <v>7.5979999999999999</v>
-      </c>
-      <c r="D10" s="4">
-        <v>6.9901599999999995</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="4">
-        <v>74.997500000000002</v>
-      </c>
-      <c r="D11" s="4">
-        <v>68.997700000000009</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="2" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="4">
-        <v>1138</v>
-      </c>
-      <c r="D12" s="4">
-        <v>1115.24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="4">
-        <v>15.42</v>
-      </c>
-      <c r="D13" s="4">
-        <v>14.9574</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="4">
-        <v>16.989999999999998</v>
-      </c>
-      <c r="D14" s="4">
-        <v>16.310399999999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="4">
-        <v>34.06</v>
-      </c>
-      <c r="D15" s="4">
-        <v>31.3352</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="4">
-        <v>48.59</v>
-      </c>
-      <c r="D16" s="4">
-        <v>46.6464</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="4">
+      <c r="C2" s="2">
         <v>6.99</v>
       </c>
-      <c r="D17" s="4">
-        <v>6.5009700000000006</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="4">
-        <v>23.82</v>
-      </c>
-      <c r="D18" s="4">
-        <v>22.8672</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" s="4">
-        <v>1.43</v>
-      </c>
-      <c r="D19" s="4">
-        <v>1.3871</v>
+      <c r="D2" s="2">
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>

--- a/promocoes.xlsx
+++ b/promocoes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael Castro\Documents\gerar-imagem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1BAC493-5FF9-4E10-8DBD-CC668C30D97F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D23ABA8-52C9-4743-A68D-DC0D6F7570B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{E5CF45C3-0614-48A6-8C4F-006EC199C177}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>descricao</t>
   </si>
@@ -42,20 +42,35 @@
     <t>valor_original</t>
   </si>
   <si>
-    <t>CAMARA 26 BUTIL BISON (CAIXA FECHADA)</t>
-  </si>
-  <si>
-    <t>03.0099</t>
+    <t>03.0101</t>
+  </si>
+  <si>
+    <t> CAMARA 29 BUTIL JOURNEY 35MM (CAIXA FECHADA 100 UN)</t>
+  </si>
+  <si>
+    <t>01.0256</t>
+  </si>
+  <si>
+    <t>PNEU 26X1.95 KENDA DH K816 PTO (AMARRADO 25 UN)</t>
+  </si>
+  <si>
+    <t>01.0257</t>
+  </si>
+  <si>
+    <t>PNEU 26X1.95 KENDA K-90 SLICK PTO (AMARRADO 25 UN)</t>
+  </si>
+  <si>
+    <t>01.0258</t>
+  </si>
+  <si>
+    <t>PNEU 26X1.1/2X2 KENDA PTO SLICK (AMARRADO 25 UN)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -70,17 +85,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF212121"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -102,18 +112,15 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -426,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A8FE7EE-E501-4B97-88C7-40543CDDBCF9}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="76.140625" bestFit="1" customWidth="1"/>
@@ -450,22 +457,67 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2">
-        <v>6.99</v>
-      </c>
-      <c r="D2" s="2">
-        <v>6.5</v>
+      <c r="C2">
+        <v>10.050000000000001</v>
+      </c>
+      <c r="D2">
+        <v>9.4499999999999993</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>30.26</v>
+      </c>
+      <c r="D3">
+        <v>28.45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>31.36</v>
+      </c>
+      <c r="D4">
+        <v>29.48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>29.8</v>
+      </c>
+      <c r="D5">
+        <v>28.02</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1" xr:uid="{0A8FE7EE-E501-4B97-88C7-40543CDDBCF9}"/>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="https://app.mercos.com/374452/representadas/614358/produtos/236160874/alterar/" xr:uid="{59096F99-9D41-43AF-9FA4-5CE8910952AB}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>